--- a/شركة الاردن الدولية للتأمين.xlsx
+++ b/شركة الاردن الدولية للتأمين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800E2CAE-569D-4A3C-BDC2-97F3FBADB8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B834A9C5-18D4-43A8-AFF4-61EE536769B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BAC0E8EA-C783-4A6D-B4DD-CD6F4F1A7BCC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="43">
   <si>
     <t>الرقم</t>
   </si>
@@ -153,6 +153,18 @@
   </si>
   <si>
     <t>محمد عبد الله الهباهبه</t>
+  </si>
+  <si>
+    <t>ميران سلامه عواد البدول</t>
+  </si>
+  <si>
+    <t>عمر سلامة البدول</t>
+  </si>
+  <si>
+    <t>قمر سليمان محمد الهلالات</t>
+  </si>
+  <si>
+    <t>عمران سلامه عواد البدول</t>
   </si>
 </sst>
 </file>
@@ -553,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDFAC0E-D819-4CBD-B6AB-2364067D1F9E}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -674,11 +686,11 @@
         <v>27.431999999999999</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J36" si="0">G3*0.94-H3</f>
+        <f t="shared" ref="J3:J46" si="0">G3*0.94-H3</f>
         <v>25.374599999999997</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L36" si="1">J3-K3</f>
+        <f t="shared" ref="L3:L46" si="1">J3-K3</f>
         <v>25.374599999999997</v>
       </c>
     </row>
@@ -1910,132 +1922,380 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="2">
         <v>1</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="2">
         <v>9931002807</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="2">
         <v>3709012</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="6">
+      <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3">
         <v>46183</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="2">
         <v>46.47</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="2">
         <v>9.2940000000000005</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="2">
         <v>37.176000000000002</v>
       </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
+      <c r="J37" s="4">
+        <f t="shared" si="0"/>
+        <v>34.387799999999999</v>
+      </c>
+      <c r="L37" s="4">
+        <f t="shared" si="1"/>
+        <v>34.387799999999999</v>
+      </c>
     </row>
     <row r="38" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="A38" s="2">
         <v>2</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="2">
         <v>9932055231</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="2">
         <v>214357</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="3">
         <v>46183</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="2">
         <v>67.959999999999994</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="2">
         <v>13.592000000000001</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="2">
         <v>54.368000000000002</v>
       </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
+      <c r="J38" s="4">
+        <f t="shared" si="0"/>
+        <v>50.290399999999991</v>
+      </c>
+      <c r="L38" s="4">
+        <f t="shared" si="1"/>
+        <v>50.290399999999991</v>
+      </c>
     </row>
     <row r="39" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="A39" s="2">
         <v>3</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="2">
         <v>2004825354</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="2">
         <v>3701544</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="6">
+      <c r="E39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="3">
         <v>46183</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="2">
         <v>24.94</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="2">
         <v>4.9880000000000004</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="2">
         <v>19.952000000000002</v>
       </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
+      <c r="J39" s="4">
+        <f t="shared" si="0"/>
+        <v>18.4556</v>
+      </c>
+      <c r="L39" s="4">
+        <f t="shared" si="1"/>
+        <v>18.4556</v>
+      </c>
     </row>
     <row r="40" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="A40" s="2">
         <v>4</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="2">
         <v>2000035533</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="2">
         <v>3266388</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="3">
         <v>46188</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="2">
         <v>47.34</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="2">
         <v>9.468</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="2">
         <v>37.872</v>
       </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
+      <c r="J40" s="4">
+        <f t="shared" si="0"/>
+        <v>35.031599999999997</v>
+      </c>
+      <c r="L40" s="4">
+        <f t="shared" si="1"/>
+        <v>35.031599999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
+        <v>1</v>
+      </c>
+      <c r="B41" s="5">
+        <v>775585</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="5">
+        <v>4730678</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46205</v>
+      </c>
+      <c r="G41" s="5">
+        <v>13.91</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1.391</v>
+      </c>
+      <c r="I41" s="5">
+        <v>12.519</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="0"/>
+        <v>11.6844</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4">
+        <f t="shared" si="1"/>
+        <v>11.6844</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>2</v>
+      </c>
+      <c r="B42" s="5">
+        <v>2003999206</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2512284</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46205</v>
+      </c>
+      <c r="G42" s="5">
+        <v>21.21</v>
+      </c>
+      <c r="H42" s="5">
+        <v>2.121</v>
+      </c>
+      <c r="I42" s="5">
+        <v>19.088999999999999</v>
+      </c>
+      <c r="J42" s="4">
+        <f t="shared" si="0"/>
+        <v>17.816400000000002</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4">
+        <f t="shared" si="1"/>
+        <v>17.816400000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
+        <v>3</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2004171316</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2762948</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46217</v>
+      </c>
+      <c r="G43" s="5">
+        <v>26.4</v>
+      </c>
+      <c r="H43" s="5">
+        <v>5.28</v>
+      </c>
+      <c r="I43" s="5">
+        <v>21.12</v>
+      </c>
+      <c r="J43" s="4">
+        <f t="shared" si="0"/>
+        <v>19.535999999999998</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4">
+        <f t="shared" si="1"/>
+        <v>19.535999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>4</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2005363249</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="5">
+        <v>5785871</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46219</v>
+      </c>
+      <c r="G44" s="5">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="H44" s="5">
+        <v>6.89</v>
+      </c>
+      <c r="I44" s="5">
+        <v>27.56</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" si="0"/>
+        <v>25.493000000000002</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4">
+        <f t="shared" si="1"/>
+        <v>25.493000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>5</v>
+      </c>
+      <c r="B45" s="5">
+        <v>785747</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2271619</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46224</v>
+      </c>
+      <c r="G45" s="5">
+        <v>29.05</v>
+      </c>
+      <c r="H45" s="5">
+        <v>2.9049999999999998</v>
+      </c>
+      <c r="I45" s="5">
+        <v>26.145</v>
+      </c>
+      <c r="J45" s="4">
+        <f t="shared" si="0"/>
+        <v>24.401999999999997</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4">
+        <f t="shared" si="1"/>
+        <v>24.401999999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>6</v>
+      </c>
+      <c r="B46" s="5">
+        <v>775585</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="5">
+        <v>7082482</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46224</v>
+      </c>
+      <c r="G46" s="5">
+        <v>33.53</v>
+      </c>
+      <c r="H46" s="5">
+        <v>3.3530000000000002</v>
+      </c>
+      <c r="I46" s="5">
+        <v>30.177</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="0"/>
+        <v>28.165199999999999</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4">
+        <f t="shared" si="1"/>
+        <v>28.165199999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/شركة الاردن الدولية للتأمين.xlsx
+++ b/شركة الاردن الدولية للتأمين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B834A9C5-18D4-43A8-AFF4-61EE536769B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8652AF-7C93-4D57-A0C4-3F078AEFFC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BAC0E8EA-C783-4A6D-B4DD-CD6F4F1A7BCC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="46">
   <si>
     <t>الرقم</t>
   </si>
@@ -165,6 +165,15 @@
   </si>
   <si>
     <t>عمران سلامه عواد البدول</t>
+  </si>
+  <si>
+    <t>سلامة عواد البدول</t>
+  </si>
+  <si>
+    <t>قمر سليمان الهلالات</t>
+  </si>
+  <si>
+    <t>محمد عبدالله الهباهبه</t>
   </si>
 </sst>
 </file>
@@ -223,12 +232,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -565,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDFAC0E-D819-4CBD-B6AB-2364067D1F9E}">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -686,11 +692,11 @@
         <v>27.431999999999999</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J46" si="0">G3*0.94-H3</f>
+        <f t="shared" ref="J3:J55" si="0">G3*0.94-H3</f>
         <v>25.374599999999997</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L46" si="1">J3-K3</f>
+        <f t="shared" ref="L3:L55" si="1">J3-K3</f>
         <v>25.374599999999997</v>
       </c>
     </row>
@@ -1949,11 +1955,11 @@
       <c r="I37" s="2">
         <v>37.176000000000002</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37">
         <f t="shared" si="0"/>
         <v>34.387799999999999</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37">
         <f t="shared" si="1"/>
         <v>34.387799999999999</v>
       </c>
@@ -1986,11 +1992,11 @@
       <c r="I38" s="2">
         <v>54.368000000000002</v>
       </c>
-      <c r="J38" s="4">
+      <c r="J38">
         <f t="shared" si="0"/>
         <v>50.290399999999991</v>
       </c>
-      <c r="L38" s="4">
+      <c r="L38">
         <f t="shared" si="1"/>
         <v>50.290399999999991</v>
       </c>
@@ -2023,11 +2029,11 @@
       <c r="I39" s="2">
         <v>19.952000000000002</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39">
         <f t="shared" si="0"/>
         <v>18.4556</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L39">
         <f t="shared" si="1"/>
         <v>18.4556</v>
       </c>
@@ -2060,241 +2066,568 @@
       <c r="I40" s="2">
         <v>37.872</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J40">
         <f t="shared" si="0"/>
         <v>35.031599999999997</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40">
         <f t="shared" si="1"/>
         <v>35.031599999999997</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="A41" s="2">
         <v>1</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="2">
         <v>775585</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="2">
         <v>4730678</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="6">
+      <c r="E41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3">
         <v>46205</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="2">
         <v>13.91</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="2">
         <v>1.391</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="2">
         <v>12.519</v>
       </c>
-      <c r="J41" s="4">
+      <c r="J41">
         <f t="shared" si="0"/>
         <v>11.6844</v>
       </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4">
+      <c r="L41">
         <f t="shared" si="1"/>
         <v>11.6844</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+      <c r="A42" s="2">
         <v>2</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="2">
         <v>2003999206</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="2">
         <v>2512284</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="6">
+      <c r="E42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="3">
         <v>46205</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="2">
         <v>21.21</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="2">
         <v>2.121</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="2">
         <v>19.088999999999999</v>
       </c>
-      <c r="J42" s="4">
+      <c r="J42">
         <f t="shared" si="0"/>
         <v>17.816400000000002</v>
       </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4">
+      <c r="L42">
         <f t="shared" si="1"/>
         <v>17.816400000000002</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="A43" s="2">
         <v>3</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="2">
         <v>2004171316</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="2">
         <v>2762948</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="6">
+      <c r="E43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3">
         <v>46217</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="2">
         <v>26.4</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="2">
         <v>5.28</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="2">
         <v>21.12</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43">
         <f t="shared" si="0"/>
         <v>19.535999999999998</v>
       </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4">
+      <c r="L43">
         <f t="shared" si="1"/>
         <v>19.535999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+      <c r="A44" s="2">
         <v>4</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="2">
         <v>2005363249</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="2">
         <v>5785871</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="6">
+      <c r="E44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="3">
         <v>46219</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="2">
         <v>34.450000000000003</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="2">
         <v>6.89</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="2">
         <v>27.56</v>
       </c>
-      <c r="J44" s="4">
+      <c r="J44">
         <f t="shared" si="0"/>
         <v>25.493000000000002</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4">
+      <c r="L44">
         <f t="shared" si="1"/>
         <v>25.493000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="A45" s="2">
         <v>5</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="2">
         <v>785747</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="2">
         <v>2271619</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="6">
+      <c r="E45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="3">
         <v>46224</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="2">
         <v>29.05</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="2">
         <v>2.9049999999999998</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="2">
         <v>26.145</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45">
         <f t="shared" si="0"/>
         <v>24.401999999999997</v>
       </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4">
+      <c r="L45">
         <f t="shared" si="1"/>
         <v>24.401999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+      <c r="A46" s="2">
         <v>6</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="2">
         <v>775585</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="2">
         <v>7082482</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="6">
+      <c r="E46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3">
         <v>46224</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="2">
         <v>33.53</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="2">
         <v>3.3530000000000002</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="2">
         <v>30.177</v>
       </c>
-      <c r="J46" s="4">
+      <c r="J46">
         <f t="shared" si="0"/>
         <v>28.165199999999999</v>
       </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4">
+      <c r="L46">
         <f t="shared" si="1"/>
         <v>28.165199999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2">
+        <v>9932055231</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="2">
+        <v>4123008</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3">
+        <v>46236</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46.2</v>
+      </c>
+      <c r="H47" s="2">
+        <v>9.24</v>
+      </c>
+      <c r="I47" s="2">
+        <v>36.96</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="0"/>
+        <v>34.187999999999995</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="1"/>
+        <v>34.187999999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>2</v>
+      </c>
+      <c r="B48" s="2">
+        <v>9931002807</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="2">
+        <v>7318938</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="3">
+        <v>46236</v>
+      </c>
+      <c r="G48" s="2">
+        <v>41.34</v>
+      </c>
+      <c r="H48" s="2">
+        <v>8.2680000000000007</v>
+      </c>
+      <c r="I48" s="2">
+        <v>33.072000000000003</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="0"/>
+        <v>30.5916</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="1"/>
+        <v>30.5916</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>3</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2004825354</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="2">
+        <v>6929834</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="3">
+        <v>46236</v>
+      </c>
+      <c r="G49" s="2">
+        <v>32.76</v>
+      </c>
+      <c r="H49" s="2">
+        <v>6.5519999999999996</v>
+      </c>
+      <c r="I49" s="2">
+        <v>26.207999999999998</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>24.242399999999996</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="1"/>
+        <v>24.242399999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>4</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2004171316</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2346872</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3">
+        <v>46237</v>
+      </c>
+      <c r="G50" s="2">
+        <v>23.92</v>
+      </c>
+      <c r="H50" s="2">
+        <v>4.7839999999999998</v>
+      </c>
+      <c r="I50" s="2">
+        <v>19.135999999999999</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="0"/>
+        <v>17.700800000000001</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="1"/>
+        <v>17.700800000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>5</v>
+      </c>
+      <c r="B51" s="2">
+        <v>9952063891</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4213978</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="3">
+        <v>46250</v>
+      </c>
+      <c r="G51" s="2">
+        <v>40.69</v>
+      </c>
+      <c r="H51" s="2">
+        <v>8.1379999999999999</v>
+      </c>
+      <c r="I51" s="2">
+        <v>32.552</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>30.110599999999998</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="1"/>
+        <v>30.110599999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>6</v>
+      </c>
+      <c r="B52" s="2">
+        <v>2004171316</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2124867</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="3">
+        <v>46255</v>
+      </c>
+      <c r="G52" s="2">
+        <v>23.53</v>
+      </c>
+      <c r="H52" s="2">
+        <v>4.7060000000000004</v>
+      </c>
+      <c r="I52" s="2">
+        <v>18.824000000000002</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>17.412199999999999</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>17.412199999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>7</v>
+      </c>
+      <c r="B53" s="2">
+        <v>2005061271</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2">
+        <v>4054541</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="3">
+        <v>46255</v>
+      </c>
+      <c r="G53" s="2">
+        <v>17.52</v>
+      </c>
+      <c r="H53" s="2">
+        <v>3.504</v>
+      </c>
+      <c r="I53" s="2">
+        <v>14.016</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>12.964799999999999</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="1"/>
+        <v>12.964799999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>8</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2005363249</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="2">
+        <v>6054670</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="3">
+        <v>46255</v>
+      </c>
+      <c r="G54" s="2">
+        <v>10.49</v>
+      </c>
+      <c r="H54" s="2">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="I54" s="2">
+        <v>8.3919999999999995</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="0"/>
+        <v>7.7625999999999999</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="1"/>
+        <v>7.7625999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>9</v>
+      </c>
+      <c r="B55" s="2">
+        <v>9951068044</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="2">
+        <v>5110890</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="3">
+        <v>46264</v>
+      </c>
+      <c r="G55" s="2">
+        <v>46.03</v>
+      </c>
+      <c r="H55" s="2">
+        <v>4.6029999999999998</v>
+      </c>
+      <c r="I55" s="2">
+        <v>41.427</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="0"/>
+        <v>38.665199999999999</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="1"/>
+        <v>38.665199999999999</v>
       </c>
     </row>
   </sheetData>
